--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est dans l'entrée. Maman pose le sac bleu. Maman dit : on met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman a dit : la gourde, le goûter, le doudou. Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip. Maman dit : c'est ce que l'adulte a dit. Léa répète : le sac est prêt.</t>
+          <t>Léa est dans l'entrée. Maman pose le sac bleu. On met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman La gourde, le goûter, le doudou. Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip. C'est ce que l'adulte a dit. Léa répète : le sac est prêt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est dans l'entrée. Maman pose le sac bleu.
+maman|On met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman
+enfant-f|La gourde, le goûter, le doudou.
+narrateur|Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip.
+maman|C'est ce que l'adulte a dit.
+narrateur|Léa répète : le sac est prêt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prépare le sac. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a mis la gourde, le goûter, le doudou. C'est ce que maman a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend le sac. Elles vont à l'école.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Léa répète : le sac est prêt.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Léa prépare le sac. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Léa a mis la gourde, le goûter, le doudou. C'est ce que maman a dit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|Maman prend le sac. Elles vont à l'école.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa prépare le sac de l'école</t>
+          <t>Les chaussures de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les chaussures rouges attendent près de la porte. Mila met la gourde, le goûter et le doudou dans le sac bleu. Maman vérifie. Elles vont à l'école.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est dans l'entrée. Maman pose le sac bleu. On met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman La gourde, le goûter, le doudou. Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip. C'est ce que l'adulte a dit. Léa répète : le sac est prêt.</t>
+          <t>Les petites chaussures rouges sont alignées. Une semelle est encore un peu froide. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. L'entrée sent le savon et le pain. Mila, on prépare le sac de l'école. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Tu la mets dans le sac ? Mila met la gourde. Bravo. La gourde est dedans. Mila prend le goûter. Le papier fait un petit bruit. Ça sent la pomme. Tu mets le goûter aussi ? Mila met le goûter. Bravo. Le goûter est dedans. Mila glisse le doudou. Il sent le coton. Il est tout doux. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Merci Mila. Le sac est prêt ? Oui, maman. Le sac est prêt. Bravo. Tu as fait du bon travail. Les chaussures rouges attendent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa est dans l'entrée. Maman pose le sac bleu.
-maman|On met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman
+          <t>narrateur|Les petites chaussures rouges sont alignées.
+narrateur|Une semelle est encore un peu froide.
+narrateur|Derrière la vitre, le village s'éveille.
+narrateur|Un vélo passe tout loin.
+narrateur|L'entrée sent le savon et le pain.
+maman|Mila, on prépare le sac de l'école.
+narrateur|En ce moment, Mila touche la sangle.
+narrateur|Maman pose le sac bleu près des chaussures.
+narrateur|Le tissu est un peu rêche.
+enfant-f|Il est bleu, maman.
+maman|Oui. On met dans le sac ce que l'adulte a dit.
+maman|La gourde, le goûter, le doudou.
 enfant-f|La gourde, le goûter, le doudou.
-narrateur|Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip.
-maman|C'est ce que l'adulte a dit.
-narrateur|Léa répète : le sac est prêt.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Mila écoute.
+narrateur|Elle prend la gourde.
+narrateur|Elle est froide contre ses doigts.
+maman|Tu la mets dans le sac ?
+narrateur|Mila met la gourde.
+maman|Bravo. La gourde est dedans.
+narrateur|Mila prend le goûter.
+narrateur|Le papier fait un petit bruit.
+narrateur|Ça sent la pomme.
+maman|Tu mets le goûter aussi ?
+narrateur|Mila met le goûter.
+maman|Bravo. Le goûter est dedans.
+narrateur|Mila glisse le doudou.
+narrateur|Il sent le coton.
+enfant-f|Il est tout doux.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|Mila ferme le zip.
+narrateur|Ça fait zzz.
+narrateur|Le sac est fermé.
+maman|Merci Mila.
+maman|Le sac est prêt ?
+enfant-f|Oui, maman. Le sac est prêt.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Les chaussures rouges attendent encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1387,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa prépare le sac. Que fait-elle ?</t>
+          <t>Mila prépare le sac. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1547,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa prépare le sac. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila prépare le sac.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1575,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a mis la gourde, le goûter, le doudou. C'est ce que maman a dit.</t>
+          <t>Mila a mis la gourde, le goûter, le doudou. C'est ce que maman a dit. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Mila pose le sac contre sa jambe. Le bleu est un peu vif. Une chaussure rouge touche le sac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,10 +1719,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a mis la gourde, le goûter, le doudou. C'est ce que maman a dit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a mis la gourde, le goûter, le doudou.
+narrateur|C'est ce que maman a dit.
+narrateur|C'est ce que l'adulte a dit.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui.
+maman|Bravo. Le sac est prêt.
+narrateur|Mila pose le sac contre sa jambe.
+narrateur|Le bleu est un peu vif.
+narrateur|Une chaussure rouge touche le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,7 +1754,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend le sac. Elles vont à l'école.</t>
+          <t>Maman prend le sac un instant. On met tes chaussures, maintenant ? Mila enfile les chaussures rouges. Tu as fini tes chaussures ? Oui, maman. Bravo. Mila reprend le sac. Elles vont à l'école. La vitre montre encore le village.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,10 +1894,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend le sac. Elles vont à l'école.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman prend le sac un instant.
+maman|On met tes chaussures, maintenant ?
+narrateur|Mila enfile les chaussures rouges.
+maman|Tu as fini tes chaussures ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Mila reprend le sac.
+narrateur|Elles vont à l'école.
+narrateur|La vitre montre encore le village.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1873,7 +1929,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,10 +2069,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les chaussures rouges tapent le chemin.
+narrateur|Le sac bleu voyage sur le dos.
+enfant-f|Le sac est prêt.
+maman|Oui. Tu as mis ce que l'adulte a dit.
+maman|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2133,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les petites chaussures rouges sont alignées. Une semelle est encore un peu froide. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. L'entrée sent le savon et le pain. Mila, on prépare le sac de l'école. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Tu la mets dans le sac ? Mila met la gourde. Bravo. La gourde est dedans. Mila prend le goûter. Le papier fait un petit bruit. Ça sent la pomme. Tu mets le goûter aussi ? Mila met le goûter. Bravo. Le goûter est dedans. Mila glisse le doudou. Il sent le coton. Il est tout doux. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Merci Mila. Le sac est prêt ? Oui, maman. Le sac est prêt. Bravo. Tu as fait du bon travail. Les chaussures rouges attendent encore.</t>
+          <t>Les petites chaussures rouges sont alignées. Une semelle est encore un peu froide. L'autre semelle est déjà sèche. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. L'entrée sent le savon et le pain. Un crochet tient le manteau de l'école. Mila, on prépare le sac de l'école. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Tu la mets dans le sac ? Mila met la gourde. Bravo. La gourde est dedans. Mila prend le goûter. Le papier fait un petit bruit. Ça sent la pomme. Tu mets le goûter aussi ? Mila met le goûter. Bravo. Le goûter est dedans. Mila glisse le doudou. Il sent le coton. Il est tout doux. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Merci Mila. Le sac est prêt ? Oui, maman. Le sac est prêt. Bravo. Tu as fait du bon travail. Les chaussures rouges attendent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1326,9 +1326,11 @@
         <is>
           <t>narrateur|Les petites chaussures rouges sont alignées.
 narrateur|Une semelle est encore un peu froide.
+narrateur|L'autre semelle est déjà sèche.
 narrateur|Derrière la vitre, le village s'éveille.
 narrateur|Un vélo passe tout loin.
 narrateur|L'entrée sent le savon et le pain.
+narrateur|Un crochet tient le manteau de l'école.
 maman|Mila, on prépare le sac de l'école.
 narrateur|En ce moment, Mila touche la sangle.
 narrateur|Maman pose le sac bleu près des chaussures.
@@ -1575,7 +1577,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a mis la gourde, le goûter, le doudou. C'est ce que maman a dit. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Mila pose le sac contre sa jambe. Le bleu est un peu vif. Une chaussure rouge touche le sac.</t>
+          <t>Mila a mis la gourde, le goûter, le doudou. C'est ce que maman a dit. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Mila pose le sac contre sa jambe. Le bleu est un peu vif. Une chaussure rouge touche le sac. Tu as mis la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1727,7 +1729,9 @@
 maman|Bravo. Le sac est prêt.
 narrateur|Mila pose le sac contre sa jambe.
 narrateur|Le bleu est un peu vif.
-narrateur|Une chaussure rouge touche le sac.</t>
+narrateur|Une chaussure rouge touche le sac.
+maman|Tu as mis la gourde, le goûter, le doudou ?
+enfant-f|Oui. C'est dans le sac.</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1758,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend le sac un instant. On met tes chaussures, maintenant ? Mila enfile les chaussures rouges. Tu as fini tes chaussures ? Oui, maman. Bravo. Mila reprend le sac. Elles vont à l'école. La vitre montre encore le village.</t>
+          <t>Maman prend le sac un instant. On met tes chaussures, maintenant ? Mila enfile les chaussures rouges. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Bravo. Mila reprend le sac. On va à l'école ? Oui. Elles vont à l'école. La vitre montre encore le village.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1897,10 +1901,13 @@
           <t>narrateur|Maman prend le sac un instant.
 maman|On met tes chaussures, maintenant ?
 narrateur|Mila enfile les chaussures rouges.
+narrateur|La semelle froide se réchauffe.
 maman|Tu as fini tes chaussures ?
 enfant-f|Oui, maman.
 maman|Bravo.
 narrateur|Mila reprend le sac.
+maman|On va à l'école ?
+enfant-f|Oui.
 narrateur|Elles vont à l'école.
 narrateur|La vitre montre encore le village.</t>
         </is>
@@ -2095,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2138,6 +2145,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les chaussures de Mila</t>
+          <t>Le dessin de Mila</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée</t>
+          <t>entrée puis chemin de l'école</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>220</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Les chaussures rouges attendent près de la porte. Mila met la gourde, le goûter et le doudou dans le sac bleu. Maman vérifie. Elles vont à l'école.</t>
+          <t>Mila veut aller à l'école montrer son dessin. Maman dit gourde, goûter, doudou. Le doudou est dans la poche du manteau. Une chaussure rouge est sous le banc. Mila met ce que maman a dit. Les chaussures tapent le chemin.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les petites chaussures rouges sont alignées. Une semelle est encore un peu froide. L'autre semelle est déjà sèche. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. L'entrée sent le savon et le pain. Un crochet tient le manteau de l'école. Mila, on prépare le sac de l'école. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Tu la mets dans le sac ? Mila met la gourde. Bravo. La gourde est dedans. Mila prend le goûter. Le papier fait un petit bruit. Ça sent la pomme. Tu mets le goûter aussi ? Mila met le goûter. Bravo. Le goûter est dedans. Mila glisse le doudou. Il sent le coton. Il est tout doux. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Merci Mila. Le sac est prêt ? Oui, maman. Le sac est prêt. Bravo. Tu as fait du bon travail. Les chaussures rouges attendent encore.</t>
+          <t>Le réveil de la cuisine fait tic. Une cuillère frappe le bol. Ça sent le savon et le pain. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. Le manteau de l'école attend au crochet. Un dessin jaune sèche près de la fenêtre. Il sent encore un peu la peinture. Une chaussette dépasse du banc. Mila, c'est le jour de l'école. Je veux montrer mon dessin. On y va. D'abord le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Mila le glisse aussi. Et mon doudou ? Le doudou n'est pas près des chaussures. Il est dans la poche du manteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa est dans l'entrée. Maman pose le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt; bleu. Maman dit : on met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman a dit : la gourde, le goûter, le doudou. Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip. Maman dit : c'est ce que l'adulte a dit. Léa répète : le sac est prêt.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le réveil de la cuisine fait tic. Une cuillère frappe le bol. Ça sent le savon et le pain. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. Le manteau de l'école attend au crochet. Un dessin jaune sèche près de la fenêtre. Il sent encore un peu la peinture. Une chaussette dépasse du banc. Mila, c'est le jour de l'école. Je veux montrer mon dessin. On y va. D'abord le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Mila le glisse aussi. Et mon doudou ? Le doudou n'est pas près des chaussures. Il est dans la poche du manteau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,17 +1324,23 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les petites chaussures rouges sont alignées.
-narrateur|Une semelle est encore un peu froide.
-narrateur|L'autre semelle est déjà sèche.
+          <t>narrateur|Le réveil de la cuisine fait tic.
+narrateur|Une cuillère frappe le bol.
+narrateur|Ça sent le savon et le pain.
 narrateur|Derrière la vitre, le village s'éveille.
 narrateur|Un vélo passe tout loin.
-narrateur|L'entrée sent le savon et le pain.
-narrateur|Un crochet tient le manteau de l'école.
-maman|Mila, on prépare le sac de l'école.
+narrateur|Le manteau de l'école attend au crochet.
+narrateur|Un dessin jaune sèche près de la fenêtre.
+narrateur|Il sent encore un peu la peinture.
+narrateur|Une chaussette dépasse du banc.
+maman|Mila, c'est le jour de l'école.
+enfant-f|Je veux montrer mon dessin.
+maman|On y va. D'abord le sac.
 narrateur|En ce moment, Mila touche la sangle.
 narrateur|Maman pose le sac bleu près des chaussures.
 narrateur|Le tissu est un peu rêche.
+narrateur|Une chaussure rouge est là.
+narrateur|L'autre n'est pas là.
 enfant-f|Il est bleu, maman.
 maman|Oui. On met dans le sac ce que l'adulte a dit.
 maman|La gourde, le goûter, le doudou.
@@ -1342,27 +1348,13 @@
 narrateur|Mila écoute.
 narrateur|Elle prend la gourde.
 narrateur|Elle est froide contre ses doigts.
-maman|Tu la mets dans le sac ?
-narrateur|Mila met la gourde.
-maman|Bravo. La gourde est dedans.
-narrateur|Mila prend le goûter.
+narrateur|Elle la met dans le sac.
+narrateur|Le goûter sent la pomme.
 narrateur|Le papier fait un petit bruit.
-narrateur|Ça sent la pomme.
-maman|Tu mets le goûter aussi ?
-narrateur|Mila met le goûter.
-maman|Bravo. Le goûter est dedans.
-narrateur|Mila glisse le doudou.
-narrateur|Il sent le coton.
-enfant-f|Il est tout doux.
-maman|Tu as mis ce que l'adulte a dit.
-narrateur|Mila ferme le zip.
-narrateur|Ça fait zzz.
-narrateur|Le sac est fermé.
-maman|Merci Mila.
-maman|Le sac est prêt ?
-enfant-f|Oui, maman. Le sac est prêt.
-maman|Bravo. Tu as fait du bon travail.
-narrateur|Les chaussures rouges attendent encore.</t>
+narrateur|Mila le glisse aussi.
+enfant-f|Et mon doudou ?
+narrateur|Le doudou n'est pas près des chaussures.
+maman|Il est dans la poche du manteau.</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1381,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mila prépare le sac. Que fait-elle ?</t>
+          <t>Mila prépare le sac. Où met-elle les affaires ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila prépare le sac. Où met-elle les affaires ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1409,7 +1401,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | mettre | elle met | dans le sac</t>
+          <t>le sac | dans le sac | elle met | mettre | la gourde | le goûter | le doudou</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1424,7 +1416,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met ce que maman a dit. Où ?</t>
+          <t>Elle met les affaires dans le sac. Où les met-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1473,7 +1465,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1550,7 +1542,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Mila prépare le sac.
-narrateur|Que fait-elle ?</t>
+narrateur|Où met-elle les affaires ?</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1569,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a mis la gourde, le goûter, le doudou. C'est ce que maman a dit. C'est ce que l'adulte a dit. Tu as fini de préparer le sac ? Oui. Bravo. Le sac est prêt. Mila pose le sac contre sa jambe. Le bleu est un peu vif. Une chaussure rouge touche le sac. Tu as mis la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
+          <t>Mila cherche dans la poche. Le doudou sent le coton. Il est tout doux. Elle le glisse dans le sac. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Le sac est prêt. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu as la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a mis la gourde, le goûter, le doudou. C'est &lt;emphasis level="moderate"&gt;ce&lt;/emphasis&gt; que maman a dit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila cherche dans la poche. Le doudou sent le coton. Il est tout doux. Elle le glisse dans le sac. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Le sac est prêt. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu as la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1721,16 +1713,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a mis la gourde, le goûter, le doudou.
-narrateur|C'est ce que maman a dit.
-narrateur|C'est ce que l'adulte a dit.
-maman|Tu as fini de préparer le sac ?
-enfant-f|Oui.
-maman|Bravo. Le sac est prêt.
+          <t>narrateur|Mila cherche dans la poche.
+narrateur|Le doudou sent le coton.
+narrateur|Il est tout doux.
+narrateur|Elle le glisse dans le sac.
+maman|Tu as mis ce que l'adulte a dit.
+narrateur|Mila ferme le zip.
+narrateur|Ça fait zzz.
+narrateur|Le sac est fermé.
+maman|Le sac est prêt ?
+enfant-f|Oui, maman. Le sac est prêt.
 narrateur|Mila pose le sac contre sa jambe.
-narrateur|Le bleu est un peu vif.
 narrateur|Une chaussure rouge touche le sac.
-maman|Tu as mis la gourde, le goûter, le doudou ?
+narrateur|Le dessin jaune attend encore.
+maman|Tu as la gourde, le goûter, le doudou ?
 enfant-f|Oui. C'est dans le sac.</t>
         </is>
       </c>
@@ -1758,12 +1754,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend le sac un instant. On met tes chaussures, maintenant ? Mila enfile les chaussures rouges. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Bravo. Mila reprend le sac. On va à l'école ? Oui. Elles vont à l'école. La vitre montre encore le village.</t>
+          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle prend aussi son dessin. On va à l'école ? Oui. Mon dessin est dans ma main. Elles vont à l'école. La vitre montre encore le village. Le chemin sent le pain du matin. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une cloche sonne tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prend le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Elles vont à l'école.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle prend aussi son dessin. On va à l'école ? Oui. Mon dessin est dans ma main. Elles vont à l'école. La vitre montre encore le village. Le chemin sent le pain du matin. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une cloche sonne tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1898,18 +1894,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend le sac un instant.
-maman|On met tes chaussures, maintenant ?
-narrateur|Mila enfile les chaussures rouges.
+          <t>maman|On met tes chaussures, maintenant.
+narrateur|Mila enfile une chaussure rouge.
+narrateur|L'autre est sous le banc.
+narrateur|Elle la tire tout doucement.
 narrateur|La semelle froide se réchauffe.
 maman|Tu as fini tes chaussures ?
 enfant-f|Oui, maman.
-maman|Bravo.
 narrateur|Mila reprend le sac.
+narrateur|Elle prend aussi son dessin.
 maman|On va à l'école ?
-enfant-f|Oui.
+enfant-f|Oui. Mon dessin est dans ma main.
 narrateur|Elles vont à l'école.
-narrateur|La vitre montre encore le village.</t>
+narrateur|La vitre montre encore le village.
+narrateur|Le chemin sent le pain du matin.
+narrateur|Mila tient le dessin tout droit.
+enfant-f|Il ne plie pas.
+maman|Tu le tiens bien.
+narrateur|Une cloche sonne tout loin.</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. Bravo, Mila. L'histoire est finie.</t>
+          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'école n'est plus loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'école n'est plus loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2004,7 +2006,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2080,7 +2082,7 @@
 narrateur|Le sac bleu voyage sur le dos.
 enfant-f|Le sac est prêt.
 maman|Oui. Tu as mis ce que l'adulte a dit.
-maman|Bravo, Mila.
+narrateur|L'école n'est plus loin.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2102,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2177,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le dessin de Mila</t>
+          <t>Le bateau de Mila</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut aller à l'école montrer son dessin. Maman dit gourde, goûter, doudou. Le doudou est dans la poche du manteau. Une chaussure rouge est sous le banc. Mila met ce que maman a dit. Les chaussures tapent le chemin.</t>
+          <t>Mila veut le bateau bleu du port. Le doudou est dans le manteau, le loquet résiste. Elle pousse, range, pose le pied sur le bois.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le réveil de la cuisine fait tic. Une cuillère frappe le bol. Ça sent le savon et le pain. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. Le manteau de l'école attend au crochet. Un dessin jaune sèche près de la fenêtre. Il sent encore un peu la peinture. Une chaussette dépasse du banc. Mila, c'est le jour de l'école. Je veux montrer mon dessin. On y va. D'abord le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Mila le glisse aussi. Et mon doudou ? Le doudou n'est pas près des chaussures. Il est dans la poche du manteau.</t>
+          <t>L'eau du port claque contre le bois. Une corde mouillée sent le sel. Les mâts bougent un tout petit peu. Dans l'appartement au-dessus du quai, ça sent le savon. Une mouette crie, tout près de la vitre. Le dessin de Mila sèche près de la fenêtre. Il sent encore un peu la peinture. Un bateau bleu attend au bout du quai. Mila, tu entends l'eau ? Oui, maman. Je veux le bateau. On y va, avec le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui, prends de l'eau pour le quai. Mila prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Glisse aussi le goûter. Mila le glisse près de l'eau. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton. Il était caché. Elle le glisse dans le sac. On ouvre ? Le loquet de la porte résiste. Il reste, maman. Pousse le petit bouton, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le réveil de la cuisine fait tic. Une cuillère frappe le bol. Ça sent le savon et le pain. Derrière la vitre, le village s'éveille. Un vélo passe tout loin. Le manteau de l'école attend au crochet. Un dessin jaune sèche près de la fenêtre. Il sent encore un peu la peinture. Une chaussette dépasse du banc. Mila, c'est le jour de l'école. Je veux montrer mon dessin. On y va. D'abord le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui. On met dans le sac ce que l'adulte a dit. La gourde, le goûter, le doudou. La gourde, le goûter, le doudou. Mila écoute. Elle prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Mila le glisse aussi. Et mon doudou ? Le doudou n'est pas près des chaussures. Il est dans la poche du manteau.</t>
+          <t>L'eau du port claque contre le bois. Une corde mouillée sent le sel. Les mâts bougent un tout petit peu. Dans l'appartement au-dessus du quai, ça sent le savon. Une mouette crie, tout près de la vitre. Le dessin de Mila sèche près de la fenêtre. Il sent encore un peu la peinture. Un bateau bleu attend au bout du quai. Mila, tu entends l'eau ? Oui, maman. Je veux le bateau. On y va, avec le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui, prends de l'eau pour le quai. Mila prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Glisse aussi le goûter. Mila le glisse près de l'eau. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton. Il était caché. Elle le glisse dans le sac. On ouvre ? Le loquet de la porte résiste. Il reste, maman. Pousse le petit bouton, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,37 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le réveil de la cuisine fait tic.
-narrateur|Une cuillère frappe le bol.
-narrateur|Ça sent le savon et le pain.
-narrateur|Derrière la vitre, le village s'éveille.
-narrateur|Un vélo passe tout loin.
-narrateur|Le manteau de l'école attend au crochet.
-narrateur|Un dessin jaune sèche près de la fenêtre.
+          <t>narrateur|L'eau du port claque contre le bois.
+narrateur|Une corde mouillée sent le sel.
+narrateur|Les mâts bougent un tout petit peu.
+narrateur|Dans l'appartement au-dessus du quai, ça sent le savon.
+narrateur|Une mouette crie, tout près de la vitre.
+narrateur|Le dessin de Mila sèche près de la fenêtre.
 narrateur|Il sent encore un peu la peinture.
-narrateur|Une chaussette dépasse du banc.
-maman|Mila, c'est le jour de l'école.
-enfant-f|Je veux montrer mon dessin.
-maman|On y va. D'abord le sac.
+narrateur|Un bateau bleu attend au bout du quai.
+maman|Mila, tu entends l'eau ?
+enfant-f|Oui, maman.
+enfant-f|Je veux le bateau.
+maman|On y va, avec le sac.
 narrateur|En ce moment, Mila touche la sangle.
 narrateur|Maman pose le sac bleu près des chaussures.
 narrateur|Le tissu est un peu rêche.
 narrateur|Une chaussure rouge est là.
 narrateur|L'autre n'est pas là.
 enfant-f|Il est bleu, maman.
-maman|Oui. On met dans le sac ce que l'adulte a dit.
-maman|La gourde, le goûter, le doudou.
-enfant-f|La gourde, le goûter, le doudou.
-narrateur|Mila écoute.
-narrateur|Elle prend la gourde.
+maman|Oui, prends de l'eau pour le quai.
+narrateur|Mila prend la gourde.
 narrateur|Elle est froide contre ses doigts.
 narrateur|Elle la met dans le sac.
 narrateur|Le goûter sent la pomme.
 narrateur|Le papier fait un petit bruit.
-narrateur|Mila le glisse aussi.
+maman|Glisse aussi le goûter.
+narrateur|Mila le glisse près de l'eau.
 enfant-f|Et mon doudou ?
 narrateur|Le doudou n'est pas près des chaussures.
-maman|Il est dans la poche du manteau.</t>
+maman|Regarde dans la poche du manteau.
+narrateur|Mila cherche dans la poche.
+narrateur|Le doudou sent le coton.
+enfant-f|Il était caché.
+narrateur|Elle le glisse dans le sac.
+maman|On ouvre ?
+narrateur|Le loquet de la porte résiste.
+enfant-f|Il reste, maman.
+maman|Pousse le petit bouton, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>le sac | dans le sac | elle met | mettre | la gourde | le goûter | le doudou</t>
+          <t>le sac | dans le sac | il met | elle met | mettre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1416,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les affaires dans le sac. Où les met-elle ?</t>
+          <t>Elle met les affaires dans le sac. Où les met Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1569,12 +1575,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila cherche dans la poche. Le doudou sent le coton. Il est tout doux. Elle le glisse dans le sac. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Le sac est prêt. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu as la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
+          <t>Mila pousse le bouton du loquet. Le métal est un peu froid. Le loquet cède, tout à coup. Il part. Merci, Mila. Mila ferme le zip du sac. Ça fait zzz. Le sac bleu est fermé. Le sac est prêt ? Oui, maman. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu prends aussi ton dessin ? Oui, pour le bateau. On cherche l'autre chaussure ? Sous le banc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila cherche dans la poche. Le doudou sent le coton. Il est tout doux. Elle le glisse dans le sac. Tu as mis ce que l'adulte a dit. Mila ferme le zip. Ça fait zzz. Le sac est fermé. Le sac est prêt ? Oui, maman. Le sac est prêt. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu as la gourde, le goûter, le doudou ? Oui. C'est dans le sac.</t>
+          <t>Mila pousse le bouton du loquet. Le métal est un peu froid. Le loquet cède, tout à coup. Il part. Merci, Mila. Mila ferme le zip du sac. Ça fait zzz. Le sac bleu est fermé. Le sac est prêt ? Oui, maman. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu prends aussi ton dessin ? Oui, pour le bateau. On cherche l'autre chaussure ? Sous le banc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1637,7 +1643,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1713,21 +1719,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila cherche dans la poche.
-narrateur|Le doudou sent le coton.
-narrateur|Il est tout doux.
-narrateur|Elle le glisse dans le sac.
-maman|Tu as mis ce que l'adulte a dit.
-narrateur|Mila ferme le zip.
+          <t>narrateur|Mila pousse le bouton du loquet.
+narrateur|Le métal est un peu froid.
+narrateur|Le loquet cède, tout à coup.
+enfant-f|Il part.
+maman|Merci, Mila.
+narrateur|Mila ferme le zip du sac.
 narrateur|Ça fait zzz.
-narrateur|Le sac est fermé.
+narrateur|Le sac bleu est fermé.
 maman|Le sac est prêt ?
-enfant-f|Oui, maman. Le sac est prêt.
+enfant-f|Oui, maman.
 narrateur|Mila pose le sac contre sa jambe.
 narrateur|Une chaussure rouge touche le sac.
 narrateur|Le dessin jaune attend encore.
-maman|Tu as la gourde, le goûter, le doudou ?
-enfant-f|Oui. C'est dans le sac.</t>
+maman|Tu prends aussi ton dessin ?
+enfant-f|Oui, pour le bateau.
+maman|On cherche l'autre chaussure ?
+enfant-f|Sous le banc.</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1762,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle prend aussi son dessin. On va à l'école ? Oui. Mon dessin est dans ma main. Elles vont à l'école. La vitre montre encore le village. Le chemin sent le pain du matin. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une cloche sonne tout loin.</t>
+          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle tient aussi son dessin. On va vers le quai ? Oui, mon dessin est dans ma main. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, tout près. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une mouette passe tout bas. L'eau claque encore contre le quai.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle prend aussi son dessin. On va à l'école ? Oui. Mon dessin est dans ma main. Elles vont à l'école. La vitre montre encore le village. Le chemin sent le pain du matin. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une cloche sonne tout loin.</t>
+          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle tient aussi son dessin. On va vers le quai ? Oui, mon dessin est dans ma main. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, tout près. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une mouette passe tout bas. L'eau claque encore contre le quai.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1822,7 +1830,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1902,16 +1910,19 @@
 maman|Tu as fini tes chaussures ?
 enfant-f|Oui, maman.
 narrateur|Mila reprend le sac.
-narrateur|Elle prend aussi son dessin.
-maman|On va à l'école ?
-enfant-f|Oui. Mon dessin est dans ma main.
-narrateur|Elles vont à l'école.
-narrateur|La vitre montre encore le village.
-narrateur|Le chemin sent le pain du matin.
+narrateur|Elle tient aussi son dessin.
+maman|On va vers le quai ?
+enfant-f|Oui, mon dessin est dans ma main.
+narrateur|Elles descendent les marches du port.
+narrateur|L'air sent le sel et le bois mouillé.
+narrateur|Le bateau bleu tape un peu l'eau.
+enfant-f|Il est là.
+maman|Oui, tout près.
 narrateur|Mila tient le dessin tout droit.
 enfant-f|Il ne plie pas.
 maman|Tu le tiens bien.
-narrateur|Une cloche sonne tout loin.</t>
+narrateur|Une mouette passe tout bas.
+narrateur|L'eau claque encore contre le quai.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'école n'est plus loin. L'histoire est finie.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Bravo, tu as préparé la sortie. L'eau du port claque encore, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures rouges tapent le chemin. Le sac bleu voyage sur le dos. Le sac est prêt. Oui. Tu as mis ce que l'adulte a dit. L'école n'est plus loin. L'histoire est finie.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Bravo, tu as préparé la sortie. L'eau du port claque encore, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1999,14 +2010,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2078,12 +2089,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Les chaussures rouges tapent le chemin.
-narrateur|Le sac bleu voyage sur le dos.
-enfant-f|Le sac est prêt.
-maman|Oui. Tu as mis ce que l'adulte a dit.
-narrateur|L'école n'est plus loin.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila pose le pied sur le bois du bateau.
+narrateur|Le bateau bouge, tout doux.
+enfant-f|On flotte, maman.
+maman|Oui, tu es arrivée.
+narrateur|Le sac bleu voyage contre sa hanche.
+narrateur|Le sel pique un peu les lèvres.
+maman|Bravo, tu as préparé la sortie.
+narrateur|L'eau du port claque encore, tout près.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2195,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée puis chemin de l'école</t>
+          <t>appartement au-dessus du quai puis bateau du port</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -1949,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Bravo, tu as préparé la sortie. L'eau du port claque encore, tout près.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Merci pour le sac, Mila. L'eau du port claque encore, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Bravo, tu as préparé la sortie. L'eau du port claque encore, tout près.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Merci pour le sac, Mila. L'eau du port claque encore, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
 maman|Oui, tu es arrivée.
 narrateur|Le sac bleu voyage contre sa hanche.
 narrateur|Le sel pique un peu les lèvres.
-maman|Bravo, tu as préparé la sortie.
+maman|Merci pour le sac, Mila.
 narrateur|L'eau du port claque encore, tout près.</t>
         </is>
       </c>
@@ -2117,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2202,6 +2202,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut le bateau bleu du port. Le doudou est dans le manteau, le loquet résiste. Elle pousse, range, pose le pied sur le bois.</t>
+          <t>Sous le plancher, le bois du quai tape. Un éclat de corde pâle brille sur le rebord. Mila veut porter son dessin jusqu'au bateau bleu, maintenant. Elle pousse tout dans le sac : le zip mord, le bateau jaune se plie. Maman s'accroupit. Une chose, puis la suivante. Un souffle glisse le dessin vers la fenêtre. Mila refuse de foncer. L'éclat de corde penche : c'est le vent. Elle ferme, glisse l'éclat, puis le dessin. Sur le bois du bateau, l'éclat porte une trace de sel.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'eau du port claque contre le bois. Une corde mouillée sent le sel. Les mâts bougent un tout petit peu. Dans l'appartement au-dessus du quai, ça sent le savon. Une mouette crie, tout près de la vitre. Le dessin de Mila sèche près de la fenêtre. Il sent encore un peu la peinture. Un bateau bleu attend au bout du quai. Mila, tu entends l'eau ? Oui, maman. Je veux le bateau. On y va, avec le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui, prends de l'eau pour le quai. Mila prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Glisse aussi le goûter. Mila le glisse près de l'eau. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton. Il était caché. Elle le glisse dans le sac. On ouvre ? Le loquet de la porte résiste. Il reste, maman. Pousse le petit bouton, tout doux.</t>
+          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un éclat de corde brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>L'eau du port claque contre le bois. Une corde mouillée sent le sel. Les mâts bougent un tout petit peu. Dans l'appartement au-dessus du quai, ça sent le savon. Une mouette crie, tout près de la vitre. Le dessin de Mila sèche près de la fenêtre. Il sent encore un peu la peinture. Un bateau bleu attend au bout du quai. Mila, tu entends l'eau ? Oui, maman. Je veux le bateau. On y va, avec le sac. En ce moment, Mila touche la sangle. Maman pose le sac bleu près des chaussures. Le tissu est un peu rêche. Une chaussure rouge est là. L'autre n'est pas là. Il est bleu, maman. Oui, prends de l'eau pour le quai. Mila prend la gourde. Elle est froide contre ses doigts. Elle la met dans le sac. Le goûter sent la pomme. Le papier fait un petit bruit. Glisse aussi le goûter. Mila le glisse près de l'eau. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton. Il était caché. Elle le glisse dans le sac. On ouvre ? Le loquet de la porte résiste. Il reste, maman. Pousse le petit bouton, tout doux.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Léa est dans l'entrée. Maman pose le &lt;emphasis&gt;sac&lt;/emphasis&gt; bleu. Maman dit : on met dans le sac ce que l'adulte a dit. L'adulte, c'est maman. Maman a dit : la gourde, le goûter, le doudou. Léa met la gourde. Elle met le goûter. Elle glisse le doudou. Elle ferme le zip. Maman dit : c'est ce que l'adulte a dit. Léa répète : le sac est prêt. [pause]</t>
+          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>éclat de corde</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,46 +1321,47 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller; emotion=impatience_curieuse; intensite=2; destinataire=enfant; sous_texte=le_bateau_tape_sous_le_plancher; tempo=naturel; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|L'eau du port claque contre le bois.
-narrateur|Une corde mouillée sent le sel.
-narrateur|Les mâts bougent un tout petit peu.
-narrateur|Dans l'appartement au-dessus du quai, ça sent le savon.
-narrateur|Une mouette crie, tout près de la vitre.
-narrateur|Le dessin de Mila sèche près de la fenêtre.
-narrateur|Il sent encore un peu la peinture.
-narrateur|Un bateau bleu attend au bout du quai.
+          <t>narrateur|Sous le plancher, le bois du quai tape.
+narrateur|Le son grimpe l'escalier, puis la pièce.
+narrateur|Dans l'appartement, ça sent le savon et le sel.
+narrateur|Une mouette crie contre la vitre.
+narrateur|Sur le rebord, un éclat de corde brille.
+narrateur|Il est pâle, raide, et il sent le sel.
+narrateur|Le vent du port l'a posé là.
+narrateur|Mila ne sait pas à quoi il servira.
+narrateur|Son dessin du bateau sèche sur la table.
+narrateur|La peinture jaune luit, un peu collante.
+narrateur|En bas, le vrai bateau bleu frappe le quai.
+enfant-f|Je veux le bateau, maintenant !
 maman|Mila, tu entends l'eau ?
 enfant-f|Oui, maman.
-enfant-f|Je veux le bateau.
+enfant-f|Il m'attend.
 maman|On y va, avec le sac.
-narrateur|En ce moment, Mila touche la sangle.
-narrateur|Maman pose le sac bleu près des chaussures.
-narrateur|Le tissu est un peu rêche.
-narrateur|Une chaussure rouge est là.
-narrateur|L'autre n'est pas là.
-enfant-f|Il est bleu, maman.
-maman|Oui, prends de l'eau pour le quai.
-narrateur|Mila prend la gourde.
-narrateur|Elle est froide contre ses doigts.
-narrateur|Elle la met dans le sac.
-narrateur|Le goûter sent la pomme.
-narrateur|Le papier fait un petit bruit.
-maman|Glisse aussi le goûter.
-narrateur|Mila le glisse près de l'eau.
-enfant-f|Et mon doudou ?
-narrateur|Le doudou n'est pas près des chaussures.
-maman|Regarde dans la poche du manteau.
-narrateur|Mila cherche dans la poche.
-narrateur|Le doudou sent le coton.
-enfant-f|Il était caché.
-narrateur|Elle le glisse dans le sac.
-maman|On ouvre ?
-narrateur|Le loquet de la porte résiste.
-enfant-f|Il reste, maman.
-maman|Pousse le petit bouton, tout doux.</t>
+narrateur|En ce moment, Mila saisit le sac bleu.
+narrateur|Le tissu gratte sous ses doigts.
+narrateur|La sangle sent le sel, comme la corde.
+maman|Prends de l'eau, pour le quai.
+narrateur|Mila prend la gourde froide.
+narrateur|Le goûter sent la pomme, dans son papier.
+enfant-f|Je mets tout, d'un coup !
+narrateur|Elle pousse gourde, pomme et dessin.
+narrateur|Le zip mord le papier du dessin.
+narrateur|Le bateau jaune se plie, de travers.
+enfant-f|Ça reste coincé !
+narrateur|Le sourire de Mila disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>eau-port,corde,plancher</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1393,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila prépare le sac. Où met-elle les affaires ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila prépare le &lt;emphasis level="moderate"&gt;sac&lt;/emphasis&gt;. Où met-elle les affaires ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léa prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Que fait-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila prépare le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Où met-elle les affaires ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1460,7 +1461,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1472,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1486,11 +1487,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1501,23 +1502,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1532,17 +1533,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=les_affaires_vont_dans_le_sac; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1575,17 +1576,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila pousse le bouton du loquet. Le métal est un peu froid. Le loquet cède, tout à coup. Il part. Merci, Mila. Mila ferme le zip du sac. Ça fait zzz. Le sac bleu est fermé. Le sac est prêt ? Oui, maman. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu prends aussi ton dessin ? Oui, pour le bateau. On cherche l'autre chaussure ? Sous le banc.</t>
+          <t>Maman s'accroupit à la même hauteur. Sors le dessin, d'abord. Mila tire le papier coincé. Le zip lâche, petit à petit. Elle pose le dessin à plat, sur la table. L'eau va au fond. Mila range la gourde froide. Le papier de la pomme glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le dessin. Le bateau jaune attend sur la table. Tu prends aussi ton dessin ? Oui, pour le vrai bateau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila pousse le bouton du loquet. Le métal est un peu froid. Le loquet cède, tout à coup. Il part. Merci, Mila. Mila ferme le zip du sac. Ça fait zzz. Le sac bleu est fermé. Le sac est prêt ? Oui, maman. Mila pose le sac contre sa jambe. Une chaussure rouge touche le sac. Le dessin jaune attend encore. Tu prends aussi ton dessin ? Oui, pour le bateau. On cherche l'autre chaussure ? Sous le banc.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman s'accroupit à la même hauteur. Sors le &lt;emphasis level="moderate"&gt;dessin&lt;/emphasis&gt;, d'abord. Mila tire le papier coincé. Le zip lâche, petit à petit. Elle pose le dessin à plat, sur la table. L'eau va au fond. Mila range la gourde froide. Le papier de la pomme glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le dessin. Le bateau jaune attend sur la table. Tu prends aussi ton dessin ? Oui, pour le vrai bateau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Léa a mis la gourde, le goûter, le doudou. C'est &lt;emphasis&gt;ce&lt;/emphasis&gt; que maman a dit. [pause]</t>
+          <t>Maman s'accroupit à la même hauteur. Sors le &lt;emphasis&gt;dessin&lt;/emphasis&gt;, d'abord. Mila tire le papier coincé. Le zip lâche, petit à petit. Elle pose le dessin à plat, sur la table. L'eau va au fond. Mila range la gourde froide. Le papier de la pomme glisse à côté. Et mon doudou ? Le doudou n'est pas près des chaussures. Regarde dans la poche du manteau. Mila cherche dans la poche. Le doudou sent le coton chaud. Il était caché. Elle le glisse dans le sac. Le zip avance, sans mordre. Il part. Le sac est prêt ? Pas le dessin. Le bateau jaune attend sur la table. Tu prends aussi ton dessin ? Oui, pour le vrai bateau. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1643,7 +1644,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1666,11 +1667,11 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>ce</t>
+          <t>dessin</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="2" t="n">
         <v>450</v>
@@ -1680,16 +1681,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1714,28 +1715,38 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=soulagement_prudent; intensite=1; destinataire=enfant; sous_texte=une_chose_puis_la_suivante; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila pousse le bouton du loquet.
-narrateur|Le métal est un peu froid.
-narrateur|Le loquet cède, tout à coup.
+          <t>narrateur|Maman s'accroupit à la même hauteur.
+maman|Sors le dessin, d'abord.
+narrateur|Mila tire le papier coincé.
+narrateur|Le zip lâche, petit à petit.
+narrateur|Elle pose le dessin à plat, sur la table.
+maman|L'eau va au fond.
+narrateur|Mila range la gourde froide.
+narrateur|Le papier de la pomme glisse à côté.
+enfant-f|Et mon doudou ?
+narrateur|Le doudou n'est pas près des chaussures.
+maman|Regarde dans la poche du manteau.
+narrateur|Mila cherche dans la poche.
+narrateur|Le doudou sent le coton chaud.
+enfant-f|Il était caché.
+narrateur|Elle le glisse dans le sac.
+narrateur|Le zip avance, sans mordre.
 enfant-f|Il part.
-maman|Merci, Mila.
-narrateur|Mila ferme le zip du sac.
-narrateur|Ça fait zzz.
-narrateur|Le sac bleu est fermé.
 maman|Le sac est prêt ?
-enfant-f|Oui, maman.
-narrateur|Mila pose le sac contre sa jambe.
-narrateur|Une chaussure rouge touche le sac.
-narrateur|Le dessin jaune attend encore.
+enfant-f|Pas le dessin.
+narrateur|Le bateau jaune attend sur la table.
 maman|Tu prends aussi ton dessin ?
-enfant-f|Oui, pour le bateau.
-maman|On cherche l'autre chaussure ?
-enfant-f|Sous le banc.</t>
+enfant-f|Oui, pour le vrai bateau.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zip,tissu</t>
         </is>
       </c>
     </row>
@@ -1762,17 +1773,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle tient aussi son dessin. On va vers le quai ? Oui, mon dessin est dans ma main. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, tout près. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une mouette passe tout bas. L'eau claque encore contre le quai.</t>
+          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'éclat de corde tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On met tes chaussures, maintenant. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire tout doucement. La semelle froide se réchauffe. Tu as fini tes chaussures ? Oui, maman. Mila reprend le sac. Elle tient aussi son dessin. On va vers le quai ? Oui, mon dessin est dans ma main. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, tout près. Mila tient le dessin tout droit. Il ne plie pas. Tu le tiens bien. Une mouette passe tout bas. L'eau claque encore contre le quai.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend le &lt;emphasis&gt;sac&lt;/emphasis&gt;. Elles vont à l'école. [pause]</t>
+          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1819,7 +1830,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1827,10 +1838,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,30 +1864,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>sac</t>
+          <t>éclat de corde</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1885,10 +1896,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1899,30 +1910,50 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=fierté_calme; intensite=2; destinataire=enfant; sous_texte=l_éclat_montre_le_vent; tempo=naturel; sourire=franc; respiration=relâchée</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On met tes chaussures, maintenant.
+          <t>narrateur|Un souffle entre par la fenêtre.
+narrateur|Le dessin glisse vers le rebord.
+enfant-f|Il va tomber !
+narrateur|Mila veut courir, le papier à la main.
+narrateur|Elle veut descendre, sans le sac.
+narrateur|Mila refuse de foncer.
+enfant-f|Attends, je regarde.
+narrateur|Sur le rebord, l'éclat de corde tremble.
+narrateur|Il penche vers la fenêtre ouverte.
+enfant-f|C'est le vent !
+maman|Le vent vient d'où ?
+enfant-f|De là, du quai.
+narrateur|Mila pousse la fenêtre.
+narrateur|Le dessin s'arrête, à plat.
+narrateur|Elle glisse l'éclat de corde dans le sac.
+narrateur|Puis le dessin, tout à la fin.
+narrateur|Le zip ferme, sans mordre.
+maman|Merci, Mila.
+maman|On cherche l'autre chaussure ?
+enfant-f|Sous le banc.
 narrateur|Mila enfile une chaussure rouge.
 narrateur|L'autre est sous le banc.
-narrateur|Elle la tire tout doucement.
-narrateur|La semelle froide se réchauffe.
+narrateur|Elle la tire, sans forcer.
 maman|Tu as fini tes chaussures ?
 enfant-f|Oui, maman.
-narrateur|Mila reprend le sac.
-narrateur|Elle tient aussi son dessin.
 maman|On va vers le quai ?
-enfant-f|Oui, mon dessin est dans ma main.
+enfant-f|Oui, le dessin est dans le sac.
 narrateur|Elles descendent les marches du port.
 narrateur|L'air sent le sel et le bois mouillé.
 narrateur|Le bateau bleu tape un peu l'eau.
 enfant-f|Il est là.
-maman|Oui, tout près.
-narrateur|Mila tient le dessin tout droit.
-enfant-f|Il ne plie pas.
-maman|Tu le tiens bien.
-narrateur|Une mouette passe tout bas.
-narrateur|L'eau claque encore contre le quai.</t>
+maman|Oui, il est près.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>vent,fenetre,marches</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1980,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Merci pour le sac, Mila. L'eau du port claque encore, tout près.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'éclat de corde porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, tout doux. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Le sel pique un peu les lèvres. Merci pour le sac, Mila. L'eau du port claque encore, tout près.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2006,18 +2037,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2026,12 +2057,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2040,17 +2071,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de corde</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2059,11 +2094,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2072,31 +2107,44 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_éclat_porte_une_trace_de_sel; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Mila pose le pied sur le bois du bateau.
-narrateur|Le bateau bouge, tout doux.
+narrateur|Le bateau bouge, léger.
 enfant-f|On flotte, maman.
 maman|Oui, tu es arrivée.
 narrateur|Le sac bleu voyage contre sa hanche.
+narrateur|Mila ouvre le sac, un peu.
+narrateur|L'éclat de corde porte une trace de sel.
+narrateur|Le dessin jaune reste plat.
+enfant-f|Il a voyagé.
+maman|Comme toi.
 narrateur|Le sel pique un peu les lèvres.
-maman|Merci pour le sac, Mila.
-narrateur|L'eau du port claque encore, tout près.</t>
+narrateur|L'eau du port tape le bois du bateau.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>bois,eau,sel</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2209,6 +2257,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.001-04.xlsx
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un éclat de corde brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
+          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un éclat de corde brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila le touche du doigt, puis le laisse. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila le touche du doigt, puis le laisse. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila ne sait pas à quoi il servira. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. [pause]</t>
+          <t>Sous le plancher, le bois du quai tape. Le son grimpe l'escalier, puis la pièce. Dans l'appartement, ça sent le savon et le sel. Une mouette crie contre la vitre. Sur le rebord, un &lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; brille. Il est pâle, raide, et il sent le sel. Le vent du port l'a posé là. Mila le touche du doigt, puis le laisse. Son dessin du bateau sèche sur la table. La peinture jaune luit, un peu collante. En bas, le vrai bateau bleu frappe le quai. Je veux le bateau, maintenant ! Mila, tu entends l'eau ? Oui, maman. Il m'attend. On y va, avec le sac. En ce moment, Mila saisit le sac bleu. Le tissu gratte sous ses doigts. La sangle sent le sel, comme la corde. Prends de l'eau, pour le quai. Mila prend la gourde froide. Le goûter sent la pomme, dans son papier. Je mets tout, d'un coup ! Elle pousse gourde, pomme et dessin. Le zip mord le papier du dessin. Le bateau jaune se plie, de travers. Ça reste coincé ! Le sourire de Mila disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
 narrateur|Sur le rebord, un éclat de corde brille.
 narrateur|Il est pâle, raide, et il sent le sel.
 narrateur|Le vent du port l'a posé là.
-narrateur|Mila ne sait pas à quoi il servira.
+narrateur|Mila le touche du doigt, puis le laisse.
 narrateur|Son dessin du bateau sèche sur la table.
 narrateur|La peinture jaune luit, un peu collante.
 narrateur|En bas, le vrai bateau bleu frappe le quai.
@@ -1773,17 +1773,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'éclat de corde tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près.</t>
+          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'éclat de corde tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, à la fin. Le zip glisse jusqu'au bout. Merci, Mila. On va vers le quai ? Oui, le dessin est dans le sac. Mila passe la sangle sur l'épaule. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Une corde mouillée frappe un anneau. Le bateau bleu tape l'eau. Il est là. Oui, il est près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, à la fin. Le zip glisse jusqu'au bout. Merci, Mila. On va vers le quai ? Oui, le dessin est dans le sac. Mila passe la sangle sur l'épaule. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Une corde mouillée frappe un anneau. Le bateau bleu tape l'eau. Il est là. Oui, il est près.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, tout à la fin. Le zip ferme, sans mordre. Merci, Mila. On cherche l'autre chaussure ? Sous le banc. Mila enfile une chaussure rouge. L'autre est sous le banc. Elle la tire, sans forcer. Tu as fini tes chaussures ? Oui, maman. On va vers le quai ? Oui, le dessin est dans le sac. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Le bateau bleu tape un peu l'eau. Il est là. Oui, il est près. [pause]</t>
+          <t>Un souffle entre par la fenêtre. Le dessin glisse vers le rebord. Il va tomber ! Mila veut courir, le papier à la main. Elle veut descendre, sans le sac. Mila refuse de foncer. Attends, je regarde. Sur le rebord, l'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; tremble. Il penche vers la fenêtre ouverte. C'est le vent ! Le vent vient d'où ? De là, du quai. Mila pousse la fenêtre. Le dessin s'arrête, à plat. Elle glisse l'éclat de corde dans le sac. Puis le dessin, à la fin. Le zip glisse jusqu'au bout. Merci, Mila. On va vers le quai ? Oui, le dessin est dans le sac. Mila passe la sangle sur l'épaule. Elles descendent les marches du port. L'air sent le sel et le bois mouillé. Une corde mouillée frappe un anneau. Le bateau bleu tape l'eau. Il est là. Oui, il est près. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AV5" s="2" t="inlineStr">
         <is>
-          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=fierté_calme; intensite=2; destinataire=enfant; sous_texte=l_éclat_montre_le_vent; tempo=naturel; sourire=franc; respiration=relâchée</t>
+          <t>arc=résolution; intention=faire_vivre_la_réussite; emotion=fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_l_éclat_dit_le_vent; tempo=naturel; sourire=franc; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1932,21 +1932,16 @@
 narrateur|Mila pousse la fenêtre.
 narrateur|Le dessin s'arrête, à plat.
 narrateur|Elle glisse l'éclat de corde dans le sac.
-narrateur|Puis le dessin, tout à la fin.
-narrateur|Le zip ferme, sans mordre.
+narrateur|Puis le dessin, à la fin.
+narrateur|Le zip glisse jusqu'au bout.
 maman|Merci, Mila.
-maman|On cherche l'autre chaussure ?
-enfant-f|Sous le banc.
-narrateur|Mila enfile une chaussure rouge.
-narrateur|L'autre est sous le banc.
-narrateur|Elle la tire, sans forcer.
-maman|Tu as fini tes chaussures ?
-enfant-f|Oui, maman.
 maman|On va vers le quai ?
 enfant-f|Oui, le dessin est dans le sac.
+narrateur|Mila passe la sangle sur l'épaule.
 narrateur|Elles descendent les marches du port.
 narrateur|L'air sent le sel et le bois mouillé.
-narrateur|Le bateau bleu tape un peu l'eau.
+narrateur|Une corde mouillée frappe un anneau.
+narrateur|Le bateau bleu tape l'eau.
 enfant-f|Il est là.
 maman|Oui, il est près.</t>
         </is>
@@ -1980,17 +1975,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'éclat de corde porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.</t>
+          <t>Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac. L'éclat de corde porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac. L'&lt;emphasis level="moderate"&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac, un peu. L'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Mila pose le pied sur le bois du bateau. Le bateau bouge, léger. On flotte, maman. Oui, tu es arrivée. Le sac bleu voyage contre sa hanche. Mila ouvre le sac. L'&lt;emphasis&gt;éclat de corde&lt;/emphasis&gt; porte une trace de sel. Le dessin jaune reste plat. Il a voyagé. Comme toi. Le sel pique un peu les lèvres. L'eau du port tape le bois du bateau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2133,7 +2128,7 @@
 enfant-f|On flotte, maman.
 maman|Oui, tu es arrivée.
 narrateur|Le sac bleu voyage contre sa hanche.
-narrateur|Mila ouvre le sac, un peu.
+narrateur|Mila ouvre le sac.
 narrateur|L'éclat de corde porte une trace de sel.
 narrateur|Le dessin jaune reste plat.
 enfant-f|Il a voyagé.
@@ -2165,7 +2160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2264,6 +2259,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
